--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_4_10.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_4_10.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>177854.7080031853</v>
+        <v>165103.0883704643</v>
       </c>
     </row>
     <row r="7">
@@ -26303,7 +26303,7 @@
         <v>53753.7027657232</v>
       </c>
       <c r="P2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
     </row>
     <row r="3">
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="C4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="D4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="E4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="F4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="G4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="H4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="I4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="J4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="K4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="L4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="M4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="N4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="O4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
       <c r="P4" t="n">
-        <v>21501.48110628928</v>
+        <v>23025.57528314837</v>
       </c>
     </row>
     <row r="5">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1375.378340566083</v>
+        <v>-2899.472517425176</v>
       </c>
       <c r="C6" t="n">
-        <v>-1375.378340566083</v>
+        <v>-2899.472517425169</v>
       </c>
       <c r="D6" t="n">
-        <v>-1375.378340566083</v>
+        <v>-2899.472517425169</v>
       </c>
       <c r="E6" t="n">
-        <v>32252.22165943392</v>
+        <v>30728.12748257482</v>
       </c>
       <c r="F6" t="n">
-        <v>32252.22165943392</v>
+        <v>30728.12748257483</v>
       </c>
       <c r="G6" t="n">
-        <v>32252.22165943392</v>
+        <v>30728.12748257483</v>
       </c>
       <c r="H6" t="n">
-        <v>32252.22165943392</v>
+        <v>30728.12748257483</v>
       </c>
       <c r="I6" t="n">
-        <v>32252.22165943392</v>
+        <v>30728.12748257482</v>
       </c>
       <c r="J6" t="n">
-        <v>32252.22165943392</v>
+        <v>30728.12748257483</v>
       </c>
       <c r="K6" t="n">
-        <v>32252.22165943392</v>
+        <v>30728.12748257482</v>
       </c>
       <c r="L6" t="n">
-        <v>32252.22165943392</v>
+        <v>30728.12748257482</v>
       </c>
       <c r="M6" t="n">
-        <v>32252.22165943392</v>
+        <v>30728.12748257482</v>
       </c>
       <c r="N6" t="n">
-        <v>32252.22165943392</v>
+        <v>30728.12748257482</v>
       </c>
       <c r="O6" t="n">
-        <v>32252.22165943392</v>
+        <v>30728.12748257483</v>
       </c>
       <c r="P6" t="n">
-        <v>32252.22165943393</v>
+        <v>30728.12748257482</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,10 +26892,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -26934,7 +26934,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,10 +26947,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -26959,34 +26959,34 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
